--- a/reports/Debug-purgatory-20260105/For The Week Ending (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260105/For The Week Ending (Prior Year)_Revenue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>DepartmentTitle</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>account</t>
-  </si>
-  <si>
-    <t>T101</t>
   </si>
   <si>
     <t>T100</t>
@@ -544,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -561,10 +558,10 @@
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -575,312 +572,298 @@
         <v>27</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2">
-        <v>83384.90</v>
+        <v>97871.13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>28</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="2">
-        <v>97871.13</v>
+        <v>26997.33</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D4" s="2">
-        <v>26997.33</v>
+        <v>500.00</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D5" s="2">
-        <v>500.00</v>
+        <v>41759.00</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D6" s="2">
-        <v>41759.00</v>
+        <v>6849.84</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="2">
-        <v>6849.84</v>
+        <v>10007.03</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="2">
-        <v>10007.03</v>
+        <v>1213.89</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="2">
-        <v>1213.89</v>
+        <v>2679.72</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D10" s="2">
-        <v>2679.72</v>
+        <v>3831.83</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="2">
-        <v>3831.83</v>
+        <v>5201.44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D12" s="2">
-        <v>5201.44</v>
+        <v>534.85</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="2">
-        <v>534.85</v>
+        <v>300.00</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D14" s="2">
-        <v>300.00</v>
+        <v>3627.82</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D15" s="2">
-        <v>3627.82</v>
+        <v>13213.93</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D16" s="2">
-        <v>13213.93</v>
+        <v>1866.38</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D17" s="2">
-        <v>1866.38</v>
+        <v>18593.12</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="2">
-        <v>18593.12</v>
+        <v>610.00</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D19" s="2">
-        <v>610.00</v>
+        <v>625.95</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D20" s="2">
-        <v>625.95</v>
+        <v>1533.34</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D21" s="2">
-        <v>1533.34</v>
+        <v>210.96</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D22" s="2">
-        <v>210.96</v>
+        <v>665.41</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D23" s="2">
-        <v>665.41</v>
+        <v>448.22</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D24" s="2">
-        <v>448.22</v>
+        <v>340.00</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D25" s="2">
-        <v>748.26</v>
+        <v>900.00</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D26" s="2">
-        <v>900.00</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="2">
-        <v>23345.95</v>
+        <v>22720.00</v>
       </c>
     </row>
   </sheetData>
